--- a/Hydroacoustics/Fillet/Copy of LLTK Fish Passage S1 - Bridge Work Time Schedule - 6.7.23.xlsx
+++ b/Hydroacoustics/Fillet/Copy of LLTK Fish Passage S1 - Bridge Work Time Schedule - 6.7.23.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khomolka\Documents\GitHub\PGST-Natural-Resources\Hydroacoustics\Fillet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D104225A-87C9-47AE-B14E-52C4485BF971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{570DC2F9-5CBE-4D15-9CC8-077D5C54BA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -109,7 +109,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,6 +121,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="6"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -146,11 +153,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="18" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,7 +445,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="60" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="58.28515625" bestFit="1" customWidth="1"/>
@@ -462,72 +472,76 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2" s="4">
         <v>45026</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="5">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>0.58333333333333337</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="6" t="s">
         <v>12</v>
       </c>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3" s="4">
         <v>45026</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="5">
         <v>0.58333333333333337</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>0.625</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="A4" s="4">
         <v>45030</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="5">
         <v>0.42708333333333331</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="A5" s="4">
         <v>45036</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="5">
         <v>0.5625</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>0.625</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="6" t="s">
         <v>7</v>
       </c>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -613,38 +627,40 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="4">
         <v>45061</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="5">
         <v>0.57291666666666663</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>0.59375</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="4">
         <v>45061</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="5">
         <v>0.59375</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>0.6875</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="6" t="s">
         <v>22</v>
       </c>
+      <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F12" t="s">
